--- a/Datos/Datos_Necesitamos.xlsx
+++ b/Datos/Datos_Necesitamos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NICO\Desktop\Universidad\Practicas\Practicas-2026-Nicolas-Garcia-Gomez\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20DEB18A-559A-4A19-804F-3AA127F30D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4937F688-A724-4D93-8F3E-7E257281B588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="71">
   <si>
     <t>Reingresos no programados en URCCPQ</t>
   </si>
@@ -57,9 +57,6 @@
     <t>*100</t>
   </si>
   <si>
-    <t>(Num de días en VMI y posición igual o superior a 20 grados</t>
-  </si>
-  <si>
     <t>Incidencia de úlceras por presion</t>
   </si>
   <si>
@@ -70,23 +67,6 @@
   </si>
   <si>
     <t>Valoracion diaria de la interrupcion de la sedacion</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">(Num días en ventilación mecánica (VM) con nivel de sedación </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>**&gt; objetivo
-que se interrumpe la sedación**</t>
-    </r>
   </si>
   <si>
     <r>
@@ -235,22 +215,13 @@
     <t>Tratamiento antibiotico empirico adecuado en la infeccion atendida</t>
   </si>
   <si>
-    <t>(Num de enfermos con infección con tratamiento antibiótico empírico</t>
-  </si>
-  <si>
     <t>Num enfermos con infeccion)</t>
   </si>
   <si>
     <t>Tasa de mortalidad estandarizada</t>
   </si>
   <si>
-    <t>HECHO</t>
-  </si>
-  <si>
     <t>Profilaxis de la ulcera por estrés en enfermos criticos que reciben nutricion enteral</t>
-  </si>
-  <si>
-    <t>(Num enfermos con riesgo de HGI con NE y que no reciben profilaxis farmacológica</t>
   </si>
   <si>
     <t>Num total enfermos con riesgo de HGI que reciben NE)</t>
@@ -266,9 +237,6 @@
   </si>
   <si>
     <t>Sedacion adecuada</t>
-  </si>
-  <si>
-    <t>(Num de enfermos con sedación continua adecuada</t>
   </si>
   <si>
     <t>Num de enfermos con sedación continua)</t>
@@ -305,35 +273,13 @@
     <t>% de ingresos que son urgentes</t>
   </si>
   <si>
-    <t>(Num de ingresos urgentes</t>
-  </si>
-  <si>
     <t>Eventos adversos durante el traslado intrahospitalario</t>
-  </si>
-  <si>
-    <t>(Num traslados intrahospitalarios con eventos adversos</t>
   </si>
   <si>
     <t>Nutricion enteral precoz</t>
   </si>
   <si>
     <t>Num de enfermos con NE)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">(Num de enfermos con NE e </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>inicio precoz</t>
-    </r>
   </si>
   <si>
     <t>Sobretransfusion de concentrados de hematies</t>
@@ -361,12 +307,6 @@
     <t>Retirada accidental del tubo endotraqueal por maniobras</t>
   </si>
   <si>
-    <t>(Num de extubaciones debidas a maniobras</t>
-  </si>
-  <si>
-    <t>Num total de días de TET)</t>
-  </si>
-  <si>
     <t>1 INDICADOR</t>
   </si>
   <si>
@@ -380,6 +320,154 @@
   </si>
   <si>
     <t>NEGRITO = INDICADOR ESPECIFICO</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">(Num de días en VMI y </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>posición igual o superior a 20 grados</t>
+    </r>
+  </si>
+  <si>
+    <t>(Fallecidos</t>
+  </si>
+  <si>
+    <r>
+      <t>(Num de ingresos</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> urgentes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">(Num traslados intrahospitalarios con </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>eventos adversos</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">(Num de extubaciones </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>debidas a maniobras</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(Num días en ventilación mecánica (VM)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> con ventana de sedacion**&gt; objetivo
+que se interrumpe la sedación**</t>
+    </r>
+  </si>
+  <si>
+    <t>(Num de enfermos con infección con tratamiento antibiótico empírico adecuado(antibioterapia y desescalada)</t>
+  </si>
+  <si>
+    <t>(Num enfermos con riesgo de HGI(corticoides, antecedentes de hemorragia gastrointestinal, cuagulopatía, insuficiencia reanl o hepática) con NE y que no reciben profilaxis farmacológica</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">(Num de enfermos con </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sedación continua adecuada</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> RASS o BIS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">(Num de enfermos con NE e </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>inicio precoz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(antes de 48h y sutura intestinal)</t>
+    </r>
+  </si>
+  <si>
+    <t>Indicador riesgo traducido(APACHE)</t>
+  </si>
+  <si>
+    <t>Num total de días de TET) = vmi</t>
   </si>
 </sst>
 </file>
@@ -483,15 +571,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -530,7 +615,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -817,25 +902,25 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="68.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="84.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="118.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="50.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7"/>
+      <c r="E1" s="6"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -861,19 +946,19 @@
       <c r="AB1" s="1"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>16</v>
+      <c r="D2" s="5" t="s">
+        <v>14</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="1"/>
@@ -901,19 +986,19 @@
       <c r="AB2" s="1"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>10</v>
+      <c r="B3" s="5" t="s">
+        <v>59</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>18</v>
+      <c r="D3" s="6" t="s">
+        <v>16</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="1"/>
@@ -941,19 +1026,19 @@
       <c r="AB3" s="1"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="1"/>
@@ -980,20 +1065,20 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:28" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>14</v>
+    <row r="5" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>13</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="1"/>
@@ -1021,19 +1106,19 @@
       <c r="AB5" s="1"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>19</v>
+      <c r="A6" s="4" t="s">
+        <v>17</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>20</v>
+      <c r="B6" s="9" t="s">
+        <v>18</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>13</v>
+      <c r="D6" s="6" t="s">
+        <v>12</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="1"/>
@@ -1061,19 +1146,19 @@
       <c r="AB6" s="1"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F7" s="1"/>
@@ -1101,19 +1186,19 @@
       <c r="AB7" s="1"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F8" s="1"/>
@@ -1141,19 +1226,19 @@
       <c r="AB8" s="1"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="1"/>
@@ -1181,19 +1266,19 @@
       <c r="AB9" s="1"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F10" s="1"/>
@@ -1221,19 +1306,19 @@
       <c r="AB10" s="1"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>33</v>
+      <c r="A11" s="4" t="s">
+        <v>31</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>34</v>
+      <c r="B11" s="9" t="s">
+        <v>65</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>35</v>
+      <c r="D11" s="6" t="s">
+        <v>32</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F11" s="1"/>
@@ -1261,17 +1346,19 @@
       <c r="AB11" s="1"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>36</v>
+      <c r="A12" s="4" t="s">
+        <v>33</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>37</v>
+      <c r="B12" s="5" t="s">
+        <v>60</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7" t="s">
+      <c r="D12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F12" s="1"/>
@@ -1299,19 +1386,19 @@
       <c r="AB12" s="1"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>38</v>
+      <c r="A13" s="4" t="s">
+        <v>34</v>
       </c>
-      <c r="B13" s="11" t="s">
-        <v>39</v>
+      <c r="B13" s="10" t="s">
+        <v>66</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>40</v>
+      <c r="D13" s="6" t="s">
+        <v>35</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F13" s="1"/>
@@ -1339,20 +1426,20 @@
       <c r="AB13" s="1"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
-        <v>41</v>
+      <c r="A14" s="4" t="s">
+        <v>36</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>42</v>
+      <c r="B14" s="5" t="s">
+        <v>37</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>18</v>
+      <c r="D14" s="6" t="s">
+        <v>16</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>43</v>
+      <c r="E14" s="6" t="s">
+        <v>38</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -1379,19 +1466,19 @@
       <c r="AB14" s="1"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
-        <v>44</v>
+      <c r="A15" s="4" t="s">
+        <v>39</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>45</v>
+      <c r="B15" s="9" t="s">
+        <v>67</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>46</v>
+      <c r="D15" s="6" t="s">
+        <v>40</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F15" s="1"/>
@@ -1419,19 +1506,19 @@
       <c r="AB15" s="1"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>47</v>
+      <c r="A16" s="4" t="s">
+        <v>41</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>48</v>
+      <c r="B16" s="5" t="s">
+        <v>42</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>49</v>
+      <c r="D16" s="5" t="s">
+        <v>43</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F16" s="1"/>
@@ -1459,19 +1546,19 @@
       <c r="AB16" s="1"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
-        <v>50</v>
+      <c r="A17" s="4" t="s">
+        <v>44</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>51</v>
+      <c r="B17" s="5" t="s">
+        <v>45</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>13</v>
+      <c r="D17" s="6" t="s">
+        <v>12</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F17" s="1"/>
@@ -1499,19 +1586,19 @@
       <c r="AB17" s="1"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
-        <v>52</v>
+      <c r="A18" s="4" t="s">
+        <v>46</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>53</v>
+      <c r="B18" s="5" t="s">
+        <v>61</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="7" t="s">
-        <v>13</v>
+      <c r="D18" s="6" t="s">
+        <v>12</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F18" s="1"/>
@@ -1539,19 +1626,19 @@
       <c r="AB18" s="1"/>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
-        <v>54</v>
+      <c r="A19" s="4" t="s">
+        <v>47</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>55</v>
+      <c r="B19" s="5" t="s">
+        <v>62</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>32</v>
+      <c r="D19" s="6" t="s">
+        <v>30</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F19" s="1"/>
@@ -1579,19 +1666,19 @@
       <c r="AB19" s="1"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
-        <v>56</v>
+      <c r="A20" s="4" t="s">
+        <v>48</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>58</v>
+      <c r="B20" s="5" t="s">
+        <v>68</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>57</v>
+      <c r="D20" s="6" t="s">
+        <v>49</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F20" s="1"/>
@@ -1619,19 +1706,19 @@
       <c r="AB20" s="1"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
-        <v>59</v>
+      <c r="A21" s="4" t="s">
+        <v>50</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>60</v>
+      <c r="B21" s="9" t="s">
+        <v>51</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>61</v>
+      <c r="D21" s="6" t="s">
+        <v>52</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="6" t="s">
         <v>9</v>
       </c>
       <c r="F21" s="1"/>
@@ -1659,19 +1746,19 @@
       <c r="AB21" s="1"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
-        <v>62</v>
+      <c r="A22" s="4" t="s">
+        <v>53</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>64</v>
+      <c r="D22" s="8" t="s">
+        <v>70</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F22" s="1"/>
@@ -1699,11 +1786,11 @@
       <c r="AB22" s="1"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A23" s="12" t="s">
-        <v>65</v>
+      <c r="A23" s="11" t="s">
+        <v>54</v>
       </c>
-      <c r="B23" s="13" t="s">
-        <v>68</v>
+      <c r="B23" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -1733,11 +1820,11 @@
       <c r="AB23" s="1"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A24" s="14" t="s">
-        <v>66</v>
+      <c r="A24" s="13" t="s">
+        <v>55</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>69</v>
+      <c r="B24" s="12" t="s">
+        <v>58</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -1767,10 +1854,10 @@
       <c r="AB24" s="1"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A25" s="15" t="s">
-        <v>67</v>
+      <c r="A25" s="14" t="s">
+        <v>56</v>
       </c>
-      <c r="B25" s="16"/>
+      <c r="B25" s="15"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -1799,7 +1886,7 @@
       <c r="AB25" s="1"/>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A26" s="3"/>
+      <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -1829,7 +1916,7 @@
       <c r="AB26" s="1"/>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A27" s="3"/>
+      <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -1859,7 +1946,7 @@
       <c r="AB27" s="1"/>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A28" s="3"/>
+      <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -1889,7 +1976,7 @@
       <c r="AB28" s="1"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A29" s="3"/>
+      <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1919,7 +2006,7 @@
       <c r="AB29" s="1"/>
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A30" s="3"/>
+      <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -1949,7 +2036,7 @@
       <c r="AB30" s="1"/>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A31" s="3"/>
+      <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -1979,7 +2066,7 @@
       <c r="AB31" s="1"/>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A32" s="3"/>
+      <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -2009,7 +2096,7 @@
       <c r="AB32" s="1"/>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A33" s="3"/>
+      <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -2039,7 +2126,7 @@
       <c r="AB33" s="1"/>
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A34" s="3"/>
+      <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -2069,7 +2156,7 @@
       <c r="AB34" s="1"/>
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A35" s="3"/>
+      <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -2099,7 +2186,7 @@
       <c r="AB35" s="1"/>
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A36" s="3"/>
+      <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -2129,7 +2216,7 @@
       <c r="AB36" s="1"/>
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A37" s="3"/>
+      <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -2159,7 +2246,7 @@
       <c r="AB37" s="1"/>
     </row>
     <row r="38" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A38" s="3"/>
+      <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -2189,7 +2276,7 @@
       <c r="AB38" s="1"/>
     </row>
     <row r="39" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A39" s="3"/>
+      <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -2219,7 +2306,7 @@
       <c r="AB39" s="1"/>
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A40" s="3"/>
+      <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -2249,7 +2336,7 @@
       <c r="AB40" s="1"/>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A41" s="3"/>
+      <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -2279,7 +2366,7 @@
       <c r="AB41" s="1"/>
     </row>
     <row r="42" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A42" s="3"/>
+      <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -2309,7 +2396,7 @@
       <c r="AB42" s="1"/>
     </row>
     <row r="43" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A43" s="3"/>
+      <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -2339,7 +2426,7 @@
       <c r="AB43" s="1"/>
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A44" s="3"/>
+      <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
@@ -2369,7 +2456,7 @@
       <c r="AB44" s="1"/>
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A45" s="3"/>
+      <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -2399,7 +2486,7 @@
       <c r="AB45" s="1"/>
     </row>
     <row r="46" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A46" s="3"/>
+      <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -2429,7 +2516,7 @@
       <c r="AB46" s="1"/>
     </row>
     <row r="47" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A47" s="3"/>
+      <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -2459,7 +2546,7 @@
       <c r="AB47" s="1"/>
     </row>
     <row r="48" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A48" s="3"/>
+      <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
@@ -2489,7 +2576,7 @@
       <c r="AB48" s="1"/>
     </row>
     <row r="49" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A49" s="3"/>
+      <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
@@ -2519,7 +2606,7 @@
       <c r="AB49" s="1"/>
     </row>
     <row r="50" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A50" s="3"/>
+      <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -2549,7 +2636,7 @@
       <c r="AB50" s="1"/>
     </row>
     <row r="51" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A51" s="3"/>
+      <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
@@ -2579,7 +2666,7 @@
       <c r="AB51" s="1"/>
     </row>
     <row r="52" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A52" s="3"/>
+      <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
@@ -2609,7 +2696,7 @@
       <c r="AB52" s="1"/>
     </row>
     <row r="53" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A53" s="3"/>
+      <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -2639,7 +2726,7 @@
       <c r="AB53" s="1"/>
     </row>
     <row r="54" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A54" s="3"/>
+      <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -2669,7 +2756,7 @@
       <c r="AB54" s="1"/>
     </row>
     <row r="55" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A55" s="3"/>
+      <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
@@ -2699,7 +2786,7 @@
       <c r="AB55" s="1"/>
     </row>
     <row r="56" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A56" s="3"/>
+      <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
@@ -2729,7 +2816,7 @@
       <c r="AB56" s="1"/>
     </row>
     <row r="57" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A57" s="3"/>
+      <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -2759,7 +2846,7 @@
       <c r="AB57" s="1"/>
     </row>
     <row r="58" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A58" s="3"/>
+      <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
@@ -2789,7 +2876,7 @@
       <c r="AB58" s="1"/>
     </row>
     <row r="59" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A59" s="3"/>
+      <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -2819,7 +2906,7 @@
       <c r="AB59" s="1"/>
     </row>
     <row r="60" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A60" s="3"/>
+      <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
@@ -2849,7 +2936,7 @@
       <c r="AB60" s="1"/>
     </row>
     <row r="61" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A61" s="3"/>
+      <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
@@ -2879,7 +2966,7 @@
       <c r="AB61" s="1"/>
     </row>
     <row r="62" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A62" s="3"/>
+      <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
@@ -2909,7 +2996,7 @@
       <c r="AB62" s="1"/>
     </row>
     <row r="63" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A63" s="3"/>
+      <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -2939,7 +3026,7 @@
       <c r="AB63" s="1"/>
     </row>
     <row r="64" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A64" s="3"/>
+      <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -2969,7 +3056,7 @@
       <c r="AB64" s="1"/>
     </row>
     <row r="65" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A65" s="3"/>
+      <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -2999,7 +3086,7 @@
       <c r="AB65" s="1"/>
     </row>
     <row r="66" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A66" s="3"/>
+      <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
@@ -3029,7 +3116,7 @@
       <c r="AB66" s="1"/>
     </row>
     <row r="67" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A67" s="3"/>
+      <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -3059,7 +3146,7 @@
       <c r="AB67" s="1"/>
     </row>
     <row r="68" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A68" s="3"/>
+      <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
@@ -3089,7 +3176,7 @@
       <c r="AB68" s="1"/>
     </row>
     <row r="69" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A69" s="3"/>
+      <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -3119,7 +3206,7 @@
       <c r="AB69" s="1"/>
     </row>
     <row r="70" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A70" s="3"/>
+      <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
@@ -3149,7 +3236,7 @@
       <c r="AB70" s="1"/>
     </row>
     <row r="71" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A71" s="3"/>
+      <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
@@ -3179,7 +3266,7 @@
       <c r="AB71" s="1"/>
     </row>
     <row r="72" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A72" s="3"/>
+      <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
@@ -3209,7 +3296,7 @@
       <c r="AB72" s="1"/>
     </row>
     <row r="73" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A73" s="3"/>
+      <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
@@ -3239,7 +3326,7 @@
       <c r="AB73" s="1"/>
     </row>
     <row r="74" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A74" s="3"/>
+      <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
@@ -3269,7 +3356,7 @@
       <c r="AB74" s="1"/>
     </row>
     <row r="75" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A75" s="3"/>
+      <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
@@ -3299,7 +3386,7 @@
       <c r="AB75" s="1"/>
     </row>
     <row r="76" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A76" s="3"/>
+      <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
@@ -3329,7 +3416,7 @@
       <c r="AB76" s="1"/>
     </row>
     <row r="77" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A77" s="3"/>
+      <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
@@ -3359,7 +3446,7 @@
       <c r="AB77" s="1"/>
     </row>
     <row r="78" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A78" s="3"/>
+      <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
@@ -3389,7 +3476,7 @@
       <c r="AB78" s="1"/>
     </row>
     <row r="79" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A79" s="3"/>
+      <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
@@ -3419,7 +3506,7 @@
       <c r="AB79" s="1"/>
     </row>
     <row r="80" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A80" s="3"/>
+      <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
@@ -3449,7 +3536,7 @@
       <c r="AB80" s="1"/>
     </row>
     <row r="81" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A81" s="3"/>
+      <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
@@ -3479,7 +3566,7 @@
       <c r="AB81" s="1"/>
     </row>
     <row r="82" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A82" s="3"/>
+      <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
@@ -3509,7 +3596,7 @@
       <c r="AB82" s="1"/>
     </row>
     <row r="83" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A83" s="3"/>
+      <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
@@ -3539,7 +3626,7 @@
       <c r="AB83" s="1"/>
     </row>
     <row r="84" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A84" s="3"/>
+      <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
@@ -3569,7 +3656,7 @@
       <c r="AB84" s="1"/>
     </row>
     <row r="85" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A85" s="3"/>
+      <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
@@ -3599,7 +3686,7 @@
       <c r="AB85" s="1"/>
     </row>
     <row r="86" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A86" s="3"/>
+      <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
@@ -3629,7 +3716,7 @@
       <c r="AB86" s="1"/>
     </row>
     <row r="87" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A87" s="3"/>
+      <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
@@ -3659,7 +3746,7 @@
       <c r="AB87" s="1"/>
     </row>
     <row r="88" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A88" s="3"/>
+      <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
@@ -3689,7 +3776,7 @@
       <c r="AB88" s="1"/>
     </row>
     <row r="89" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A89" s="3"/>
+      <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
@@ -3719,7 +3806,7 @@
       <c r="AB89" s="1"/>
     </row>
     <row r="90" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A90" s="3"/>
+      <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
@@ -3749,7 +3836,7 @@
       <c r="AB90" s="1"/>
     </row>
     <row r="91" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A91" s="3"/>
+      <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
@@ -3779,7 +3866,7 @@
       <c r="AB91" s="1"/>
     </row>
     <row r="92" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A92" s="3"/>
+      <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
@@ -3809,7 +3896,7 @@
       <c r="AB92" s="1"/>
     </row>
     <row r="93" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A93" s="3"/>
+      <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
@@ -3839,7 +3926,7 @@
       <c r="AB93" s="1"/>
     </row>
     <row r="94" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A94" s="3"/>
+      <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
@@ -3869,7 +3956,7 @@
       <c r="AB94" s="1"/>
     </row>
     <row r="95" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A95" s="3"/>
+      <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
@@ -3899,7 +3986,7 @@
       <c r="AB95" s="1"/>
     </row>
     <row r="96" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A96" s="3"/>
+      <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
@@ -3929,7 +4016,7 @@
       <c r="AB96" s="1"/>
     </row>
     <row r="97" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A97" s="3"/>
+      <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
@@ -3959,7 +4046,7 @@
       <c r="AB97" s="1"/>
     </row>
     <row r="98" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A98" s="3"/>
+      <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
@@ -3989,7 +4076,7 @@
       <c r="AB98" s="1"/>
     </row>
     <row r="99" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A99" s="3"/>
+      <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
@@ -4019,7 +4106,7 @@
       <c r="AB99" s="1"/>
     </row>
     <row r="100" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A100" s="3"/>
+      <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
@@ -4049,7 +4136,7 @@
       <c r="AB100" s="1"/>
     </row>
     <row r="101" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A101" s="3"/>
+      <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
@@ -4079,7 +4166,7 @@
       <c r="AB101" s="1"/>
     </row>
     <row r="102" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A102" s="3"/>
+      <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
@@ -4109,7 +4196,7 @@
       <c r="AB102" s="1"/>
     </row>
     <row r="103" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A103" s="3"/>
+      <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
@@ -4139,7 +4226,7 @@
       <c r="AB103" s="1"/>
     </row>
     <row r="104" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A104" s="3"/>
+      <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
@@ -4169,7 +4256,7 @@
       <c r="AB104" s="1"/>
     </row>
     <row r="105" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A105" s="3"/>
+      <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
@@ -4199,7 +4286,7 @@
       <c r="AB105" s="1"/>
     </row>
     <row r="106" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A106" s="3"/>
+      <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
@@ -4229,7 +4316,7 @@
       <c r="AB106" s="1"/>
     </row>
     <row r="107" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A107" s="3"/>
+      <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
@@ -4259,7 +4346,7 @@
       <c r="AB107" s="1"/>
     </row>
     <row r="108" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A108" s="3"/>
+      <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
@@ -4289,7 +4376,7 @@
       <c r="AB108" s="1"/>
     </row>
     <row r="109" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A109" s="3"/>
+      <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
@@ -4319,7 +4406,7 @@
       <c r="AB109" s="1"/>
     </row>
     <row r="110" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A110" s="3"/>
+      <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
@@ -4349,7 +4436,7 @@
       <c r="AB110" s="1"/>
     </row>
     <row r="111" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A111" s="3"/>
+      <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
@@ -4379,7 +4466,7 @@
       <c r="AB111" s="1"/>
     </row>
     <row r="112" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A112" s="3"/>
+      <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
@@ -4409,7 +4496,7 @@
       <c r="AB112" s="1"/>
     </row>
     <row r="113" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A113" s="3"/>
+      <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
@@ -4439,7 +4526,7 @@
       <c r="AB113" s="1"/>
     </row>
     <row r="114" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A114" s="3"/>
+      <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
@@ -4469,7 +4556,7 @@
       <c r="AB114" s="1"/>
     </row>
     <row r="115" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A115" s="3"/>
+      <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
@@ -4499,7 +4586,7 @@
       <c r="AB115" s="1"/>
     </row>
     <row r="116" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A116" s="3"/>
+      <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
@@ -4529,7 +4616,7 @@
       <c r="AB116" s="1"/>
     </row>
     <row r="117" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A117" s="3"/>
+      <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
@@ -4559,7 +4646,7 @@
       <c r="AB117" s="1"/>
     </row>
     <row r="118" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A118" s="3"/>
+      <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
@@ -4589,7 +4676,7 @@
       <c r="AB118" s="1"/>
     </row>
     <row r="119" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A119" s="3"/>
+      <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
@@ -4619,7 +4706,7 @@
       <c r="AB119" s="1"/>
     </row>
     <row r="120" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A120" s="3"/>
+      <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
@@ -4649,7 +4736,7 @@
       <c r="AB120" s="1"/>
     </row>
     <row r="121" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A121" s="3"/>
+      <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
@@ -4679,7 +4766,7 @@
       <c r="AB121" s="1"/>
     </row>
     <row r="122" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A122" s="3"/>
+      <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
@@ -4709,7 +4796,7 @@
       <c r="AB122" s="1"/>
     </row>
     <row r="123" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A123" s="3"/>
+      <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
@@ -4739,7 +4826,7 @@
       <c r="AB123" s="1"/>
     </row>
     <row r="124" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A124" s="3"/>
+      <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
@@ -4769,7 +4856,7 @@
       <c r="AB124" s="1"/>
     </row>
     <row r="125" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A125" s="3"/>
+      <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
@@ -4799,7 +4886,7 @@
       <c r="AB125" s="1"/>
     </row>
     <row r="126" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A126" s="3"/>
+      <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
       <c r="D126" s="2"/>
@@ -4829,7 +4916,7 @@
       <c r="AB126" s="1"/>
     </row>
     <row r="127" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A127" s="3"/>
+      <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
@@ -4859,7 +4946,7 @@
       <c r="AB127" s="1"/>
     </row>
     <row r="128" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A128" s="3"/>
+      <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
@@ -4889,7 +4976,7 @@
       <c r="AB128" s="1"/>
     </row>
     <row r="129" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A129" s="3"/>
+      <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
@@ -4919,7 +5006,7 @@
       <c r="AB129" s="1"/>
     </row>
     <row r="130" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A130" s="3"/>
+      <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
@@ -4949,7 +5036,7 @@
       <c r="AB130" s="1"/>
     </row>
     <row r="131" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A131" s="3"/>
+      <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
       <c r="D131" s="2"/>
@@ -4979,7 +5066,7 @@
       <c r="AB131" s="1"/>
     </row>
     <row r="132" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A132" s="3"/>
+      <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
@@ -5009,7 +5096,7 @@
       <c r="AB132" s="1"/>
     </row>
     <row r="133" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A133" s="3"/>
+      <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
@@ -5039,7 +5126,7 @@
       <c r="AB133" s="1"/>
     </row>
     <row r="134" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A134" s="3"/>
+      <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
@@ -5069,7 +5156,7 @@
       <c r="AB134" s="1"/>
     </row>
     <row r="135" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A135" s="3"/>
+      <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
@@ -5099,7 +5186,7 @@
       <c r="AB135" s="1"/>
     </row>
     <row r="136" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A136" s="3"/>
+      <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
@@ -5129,7 +5216,7 @@
       <c r="AB136" s="1"/>
     </row>
     <row r="137" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A137" s="3"/>
+      <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
       <c r="D137" s="2"/>
@@ -5159,7 +5246,7 @@
       <c r="AB137" s="1"/>
     </row>
     <row r="138" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A138" s="3"/>
+      <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
@@ -5189,7 +5276,7 @@
       <c r="AB138" s="1"/>
     </row>
     <row r="139" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A139" s="3"/>
+      <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
@@ -5219,7 +5306,7 @@
       <c r="AB139" s="1"/>
     </row>
     <row r="140" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A140" s="3"/>
+      <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
@@ -5249,7 +5336,7 @@
       <c r="AB140" s="1"/>
     </row>
     <row r="141" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A141" s="3"/>
+      <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
       <c r="D141" s="2"/>
@@ -5279,7 +5366,7 @@
       <c r="AB141" s="1"/>
     </row>
     <row r="142" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A142" s="3"/>
+      <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
@@ -5309,7 +5396,7 @@
       <c r="AB142" s="1"/>
     </row>
     <row r="143" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A143" s="3"/>
+      <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
@@ -5339,7 +5426,7 @@
       <c r="AB143" s="1"/>
     </row>
     <row r="144" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A144" s="3"/>
+      <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
@@ -5369,7 +5456,7 @@
       <c r="AB144" s="1"/>
     </row>
     <row r="145" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A145" s="3"/>
+      <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
@@ -5399,7 +5486,7 @@
       <c r="AB145" s="1"/>
     </row>
     <row r="146" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A146" s="3"/>
+      <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
@@ -5429,7 +5516,7 @@
       <c r="AB146" s="1"/>
     </row>
     <row r="147" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A147" s="3"/>
+      <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
@@ -5459,7 +5546,7 @@
       <c r="AB147" s="1"/>
     </row>
     <row r="148" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A148" s="3"/>
+      <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
       <c r="D148" s="2"/>
@@ -5489,7 +5576,7 @@
       <c r="AB148" s="1"/>
     </row>
     <row r="149" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A149" s="3"/>
+      <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
       <c r="D149" s="2"/>
@@ -5519,7 +5606,7 @@
       <c r="AB149" s="1"/>
     </row>
     <row r="150" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A150" s="3"/>
+      <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
@@ -5549,7 +5636,7 @@
       <c r="AB150" s="1"/>
     </row>
     <row r="151" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A151" s="3"/>
+      <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
       <c r="D151" s="2"/>
@@ -5579,7 +5666,7 @@
       <c r="AB151" s="1"/>
     </row>
     <row r="152" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A152" s="3"/>
+      <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
       <c r="D152" s="2"/>
@@ -5609,7 +5696,7 @@
       <c r="AB152" s="1"/>
     </row>
     <row r="153" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A153" s="3"/>
+      <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
       <c r="D153" s="2"/>
@@ -5639,7 +5726,7 @@
       <c r="AB153" s="1"/>
     </row>
     <row r="154" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A154" s="3"/>
+      <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
       <c r="D154" s="2"/>
@@ -5669,7 +5756,7 @@
       <c r="AB154" s="1"/>
     </row>
     <row r="155" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A155" s="3"/>
+      <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
       <c r="D155" s="2"/>
@@ -5699,7 +5786,7 @@
       <c r="AB155" s="1"/>
     </row>
     <row r="156" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A156" s="3"/>
+      <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
       <c r="D156" s="2"/>
@@ -5729,7 +5816,7 @@
       <c r="AB156" s="1"/>
     </row>
     <row r="157" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A157" s="3"/>
+      <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
       <c r="D157" s="2"/>
@@ -5759,7 +5846,7 @@
       <c r="AB157" s="1"/>
     </row>
     <row r="158" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A158" s="3"/>
+      <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
       <c r="D158" s="2"/>
@@ -5789,7 +5876,7 @@
       <c r="AB158" s="1"/>
     </row>
     <row r="159" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A159" s="3"/>
+      <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
       <c r="D159" s="2"/>
@@ -5819,7 +5906,7 @@
       <c r="AB159" s="1"/>
     </row>
     <row r="160" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A160" s="3"/>
+      <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
       <c r="D160" s="2"/>
@@ -5849,7 +5936,7 @@
       <c r="AB160" s="1"/>
     </row>
     <row r="161" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A161" s="3"/>
+      <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
       <c r="D161" s="2"/>
@@ -5879,7 +5966,7 @@
       <c r="AB161" s="1"/>
     </row>
     <row r="162" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A162" s="3"/>
+      <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
       <c r="D162" s="2"/>
@@ -5909,7 +5996,7 @@
       <c r="AB162" s="1"/>
     </row>
     <row r="163" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A163" s="3"/>
+      <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
       <c r="D163" s="2"/>
@@ -5939,7 +6026,7 @@
       <c r="AB163" s="1"/>
     </row>
     <row r="164" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A164" s="3"/>
+      <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
       <c r="D164" s="2"/>
@@ -5969,7 +6056,7 @@
       <c r="AB164" s="1"/>
     </row>
     <row r="165" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A165" s="3"/>
+      <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
       <c r="D165" s="2"/>
@@ -5999,7 +6086,7 @@
       <c r="AB165" s="1"/>
     </row>
     <row r="166" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A166" s="3"/>
+      <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
       <c r="D166" s="2"/>
@@ -6029,7 +6116,7 @@
       <c r="AB166" s="1"/>
     </row>
     <row r="167" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A167" s="3"/>
+      <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
       <c r="D167" s="2"/>
@@ -6059,7 +6146,7 @@
       <c r="AB167" s="1"/>
     </row>
     <row r="168" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A168" s="3"/>
+      <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
       <c r="D168" s="2"/>
@@ -6089,7 +6176,7 @@
       <c r="AB168" s="1"/>
     </row>
     <row r="169" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A169" s="3"/>
+      <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
       <c r="D169" s="2"/>
@@ -6119,7 +6206,7 @@
       <c r="AB169" s="1"/>
     </row>
     <row r="170" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A170" s="3"/>
+      <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
       <c r="D170" s="2"/>
@@ -6149,7 +6236,7 @@
       <c r="AB170" s="1"/>
     </row>
     <row r="171" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A171" s="3"/>
+      <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
@@ -6179,7 +6266,7 @@
       <c r="AB171" s="1"/>
     </row>
     <row r="172" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A172" s="3"/>
+      <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
@@ -6209,7 +6296,7 @@
       <c r="AB172" s="1"/>
     </row>
     <row r="173" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A173" s="3"/>
+      <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
       <c r="D173" s="2"/>
@@ -6239,7 +6326,7 @@
       <c r="AB173" s="1"/>
     </row>
     <row r="174" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A174" s="3"/>
+      <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
@@ -6269,7 +6356,7 @@
       <c r="AB174" s="1"/>
     </row>
     <row r="175" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A175" s="3"/>
+      <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
       <c r="D175" s="2"/>
@@ -6299,7 +6386,7 @@
       <c r="AB175" s="1"/>
     </row>
     <row r="176" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A176" s="3"/>
+      <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
       <c r="D176" s="2"/>
@@ -6329,7 +6416,7 @@
       <c r="AB176" s="1"/>
     </row>
     <row r="177" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A177" s="3"/>
+      <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
@@ -6359,7 +6446,7 @@
       <c r="AB177" s="1"/>
     </row>
     <row r="178" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A178" s="3"/>
+      <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
@@ -6389,7 +6476,7 @@
       <c r="AB178" s="1"/>
     </row>
     <row r="179" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A179" s="3"/>
+      <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
       <c r="D179" s="2"/>
@@ -6419,7 +6506,7 @@
       <c r="AB179" s="1"/>
     </row>
     <row r="180" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A180" s="3"/>
+      <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
       <c r="D180" s="2"/>
@@ -6449,7 +6536,7 @@
       <c r="AB180" s="1"/>
     </row>
     <row r="181" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A181" s="3"/>
+      <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
       <c r="D181" s="2"/>
@@ -6479,7 +6566,7 @@
       <c r="AB181" s="1"/>
     </row>
     <row r="182" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A182" s="3"/>
+      <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
       <c r="D182" s="2"/>
@@ -6509,7 +6596,7 @@
       <c r="AB182" s="1"/>
     </row>
     <row r="183" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A183" s="3"/>
+      <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
       <c r="D183" s="2"/>
@@ -6539,7 +6626,7 @@
       <c r="AB183" s="1"/>
     </row>
     <row r="184" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A184" s="3"/>
+      <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
       <c r="D184" s="2"/>
@@ -6569,7 +6656,7 @@
       <c r="AB184" s="1"/>
     </row>
     <row r="185" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A185" s="3"/>
+      <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
       <c r="D185" s="2"/>
@@ -6599,7 +6686,7 @@
       <c r="AB185" s="1"/>
     </row>
     <row r="186" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A186" s="3"/>
+      <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
@@ -6629,7 +6716,7 @@
       <c r="AB186" s="1"/>
     </row>
     <row r="187" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A187" s="3"/>
+      <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
       <c r="D187" s="2"/>
@@ -6659,7 +6746,7 @@
       <c r="AB187" s="1"/>
     </row>
     <row r="188" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A188" s="3"/>
+      <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
       <c r="D188" s="2"/>
@@ -6689,7 +6776,7 @@
       <c r="AB188" s="1"/>
     </row>
     <row r="189" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A189" s="3"/>
+      <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
@@ -6719,7 +6806,7 @@
       <c r="AB189" s="1"/>
     </row>
     <row r="190" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A190" s="3"/>
+      <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
       <c r="D190" s="2"/>
@@ -6749,7 +6836,7 @@
       <c r="AB190" s="1"/>
     </row>
     <row r="191" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A191" s="3"/>
+      <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
       <c r="D191" s="2"/>
@@ -6779,7 +6866,7 @@
       <c r="AB191" s="1"/>
     </row>
     <row r="192" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A192" s="3"/>
+      <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
       <c r="D192" s="2"/>
@@ -6809,7 +6896,7 @@
       <c r="AB192" s="1"/>
     </row>
     <row r="193" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A193" s="3"/>
+      <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
       <c r="D193" s="2"/>
@@ -6839,7 +6926,7 @@
       <c r="AB193" s="1"/>
     </row>
     <row r="194" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A194" s="3"/>
+      <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
       <c r="D194" s="2"/>
@@ -6869,7 +6956,7 @@
       <c r="AB194" s="1"/>
     </row>
     <row r="195" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A195" s="3"/>
+      <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
       <c r="D195" s="2"/>
@@ -6899,7 +6986,7 @@
       <c r="AB195" s="1"/>
     </row>
     <row r="196" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A196" s="3"/>
+      <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
       <c r="D196" s="2"/>
@@ -6929,7 +7016,7 @@
       <c r="AB196" s="1"/>
     </row>
     <row r="197" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A197" s="3"/>
+      <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
       <c r="D197" s="2"/>
@@ -6959,7 +7046,7 @@
       <c r="AB197" s="1"/>
     </row>
     <row r="198" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A198" s="3"/>
+      <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
@@ -6989,7 +7076,7 @@
       <c r="AB198" s="1"/>
     </row>
     <row r="199" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A199" s="3"/>
+      <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
       <c r="D199" s="2"/>
@@ -7019,7 +7106,7 @@
       <c r="AB199" s="1"/>
     </row>
     <row r="200" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A200" s="3"/>
+      <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
@@ -7049,7 +7136,7 @@
       <c r="AB200" s="1"/>
     </row>
     <row r="201" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A201" s="3"/>
+      <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
       <c r="D201" s="2"/>
@@ -7079,7 +7166,7 @@
       <c r="AB201" s="1"/>
     </row>
     <row r="202" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A202" s="3"/>
+      <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
       <c r="D202" s="2"/>
@@ -7109,7 +7196,7 @@
       <c r="AB202" s="1"/>
     </row>
     <row r="203" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A203" s="3"/>
+      <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
       <c r="D203" s="2"/>
@@ -7139,7 +7226,7 @@
       <c r="AB203" s="1"/>
     </row>
     <row r="204" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A204" s="3"/>
+      <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
       <c r="D204" s="2"/>
@@ -7169,7 +7256,7 @@
       <c r="AB204" s="1"/>
     </row>
     <row r="205" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A205" s="3"/>
+      <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
@@ -7199,7 +7286,7 @@
       <c r="AB205" s="1"/>
     </row>
     <row r="206" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A206" s="3"/>
+      <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
       <c r="D206" s="2"/>
@@ -7229,7 +7316,7 @@
       <c r="AB206" s="1"/>
     </row>
     <row r="207" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A207" s="3"/>
+      <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
       <c r="D207" s="2"/>
@@ -7259,7 +7346,7 @@
       <c r="AB207" s="1"/>
     </row>
     <row r="208" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A208" s="3"/>
+      <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
       <c r="D208" s="2"/>
@@ -7289,7 +7376,7 @@
       <c r="AB208" s="1"/>
     </row>
     <row r="209" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A209" s="3"/>
+      <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
       <c r="D209" s="2"/>
@@ -7319,7 +7406,7 @@
       <c r="AB209" s="1"/>
     </row>
     <row r="210" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A210" s="3"/>
+      <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
       <c r="D210" s="2"/>
@@ -7349,7 +7436,7 @@
       <c r="AB210" s="1"/>
     </row>
     <row r="211" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A211" s="3"/>
+      <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
       <c r="D211" s="2"/>
@@ -7379,7 +7466,7 @@
       <c r="AB211" s="1"/>
     </row>
     <row r="212" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A212" s="3"/>
+      <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
       <c r="D212" s="2"/>
@@ -7409,7 +7496,7 @@
       <c r="AB212" s="1"/>
     </row>
     <row r="213" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A213" s="3"/>
+      <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
       <c r="D213" s="2"/>
@@ -7439,7 +7526,7 @@
       <c r="AB213" s="1"/>
     </row>
     <row r="214" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A214" s="3"/>
+      <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
       <c r="D214" s="2"/>
@@ -7469,7 +7556,7 @@
       <c r="AB214" s="1"/>
     </row>
     <row r="215" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A215" s="3"/>
+      <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
       <c r="D215" s="2"/>
@@ -7499,7 +7586,7 @@
       <c r="AB215" s="1"/>
     </row>
     <row r="216" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A216" s="3"/>
+      <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
       <c r="D216" s="2"/>
@@ -7529,7 +7616,7 @@
       <c r="AB216" s="1"/>
     </row>
     <row r="217" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A217" s="3"/>
+      <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
       <c r="D217" s="2"/>
@@ -7559,7 +7646,7 @@
       <c r="AB217" s="1"/>
     </row>
     <row r="218" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A218" s="3"/>
+      <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
       <c r="D218" s="2"/>
@@ -7589,7 +7676,7 @@
       <c r="AB218" s="1"/>
     </row>
     <row r="219" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A219" s="3"/>
+      <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
       <c r="D219" s="2"/>
@@ -7619,7 +7706,7 @@
       <c r="AB219" s="1"/>
     </row>
     <row r="220" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A220" s="3"/>
+      <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
       <c r="D220" s="2"/>
@@ -7649,7 +7736,7 @@
       <c r="AB220" s="1"/>
     </row>
     <row r="221" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A221" s="3"/>
+      <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
       <c r="D221" s="2"/>
@@ -7679,7 +7766,7 @@
       <c r="AB221" s="1"/>
     </row>
     <row r="222" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A222" s="3"/>
+      <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
       <c r="D222" s="2"/>
@@ -7709,7 +7796,7 @@
       <c r="AB222" s="1"/>
     </row>
     <row r="223" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A223" s="3"/>
+      <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
       <c r="D223" s="2"/>
@@ -7739,7 +7826,7 @@
       <c r="AB223" s="1"/>
     </row>
     <row r="224" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A224" s="3"/>
+      <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
       <c r="D224" s="2"/>
@@ -7769,7 +7856,7 @@
       <c r="AB224" s="1"/>
     </row>
     <row r="225" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A225" s="3"/>
+      <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
       <c r="D225" s="2"/>
@@ -7799,7 +7886,7 @@
       <c r="AB225" s="1"/>
     </row>
     <row r="226" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A226" s="3"/>
+      <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
       <c r="D226" s="2"/>
@@ -7829,7 +7916,7 @@
       <c r="AB226" s="1"/>
     </row>
     <row r="227" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A227" s="3"/>
+      <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
       <c r="D227" s="2"/>
@@ -7859,7 +7946,7 @@
       <c r="AB227" s="1"/>
     </row>
     <row r="228" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A228" s="3"/>
+      <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
       <c r="D228" s="2"/>
@@ -7889,7 +7976,7 @@
       <c r="AB228" s="1"/>
     </row>
     <row r="229" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A229" s="3"/>
+      <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
       <c r="D229" s="2"/>
@@ -7919,7 +8006,7 @@
       <c r="AB229" s="1"/>
     </row>
     <row r="230" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A230" s="3"/>
+      <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
       <c r="D230" s="2"/>
@@ -7949,7 +8036,7 @@
       <c r="AB230" s="1"/>
     </row>
     <row r="231" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A231" s="3"/>
+      <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
       <c r="D231" s="2"/>
@@ -7979,7 +8066,7 @@
       <c r="AB231" s="1"/>
     </row>
     <row r="232" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A232" s="3"/>
+      <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
       <c r="D232" s="2"/>
@@ -8009,7 +8096,7 @@
       <c r="AB232" s="1"/>
     </row>
     <row r="233" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A233" s="3"/>
+      <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
       <c r="D233" s="2"/>
@@ -8039,7 +8126,7 @@
       <c r="AB233" s="1"/>
     </row>
     <row r="234" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A234" s="3"/>
+      <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
       <c r="D234" s="2"/>
@@ -8069,7 +8156,7 @@
       <c r="AB234" s="1"/>
     </row>
     <row r="235" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A235" s="3"/>
+      <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
       <c r="D235" s="2"/>
@@ -8099,7 +8186,7 @@
       <c r="AB235" s="1"/>
     </row>
     <row r="236" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A236" s="3"/>
+      <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
       <c r="D236" s="2"/>
@@ -8129,7 +8216,7 @@
       <c r="AB236" s="1"/>
     </row>
     <row r="237" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A237" s="3"/>
+      <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
       <c r="D237" s="2"/>
@@ -8159,7 +8246,7 @@
       <c r="AB237" s="1"/>
     </row>
     <row r="238" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A238" s="3"/>
+      <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
       <c r="D238" s="2"/>
@@ -8189,7 +8276,7 @@
       <c r="AB238" s="1"/>
     </row>
     <row r="239" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A239" s="3"/>
+      <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
       <c r="D239" s="2"/>
@@ -8219,7 +8306,7 @@
       <c r="AB239" s="1"/>
     </row>
     <row r="240" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A240" s="3"/>
+      <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
       <c r="D240" s="2"/>
@@ -8249,7 +8336,7 @@
       <c r="AB240" s="1"/>
     </row>
     <row r="241" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A241" s="3"/>
+      <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
       <c r="D241" s="2"/>
@@ -8279,7 +8366,7 @@
       <c r="AB241" s="1"/>
     </row>
     <row r="242" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A242" s="3"/>
+      <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
       <c r="D242" s="2"/>
@@ -8309,7 +8396,7 @@
       <c r="AB242" s="1"/>
     </row>
     <row r="243" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A243" s="3"/>
+      <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
       <c r="D243" s="2"/>
@@ -8339,7 +8426,7 @@
       <c r="AB243" s="1"/>
     </row>
     <row r="244" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A244" s="3"/>
+      <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
       <c r="D244" s="2"/>
@@ -8369,7 +8456,7 @@
       <c r="AB244" s="1"/>
     </row>
     <row r="245" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A245" s="3"/>
+      <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
       <c r="D245" s="2"/>
@@ -8399,7 +8486,7 @@
       <c r="AB245" s="1"/>
     </row>
     <row r="246" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A246" s="3"/>
+      <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
       <c r="D246" s="2"/>
@@ -8429,7 +8516,7 @@
       <c r="AB246" s="1"/>
     </row>
     <row r="247" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A247" s="3"/>
+      <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
       <c r="D247" s="2"/>
@@ -8459,7 +8546,7 @@
       <c r="AB247" s="1"/>
     </row>
     <row r="248" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A248" s="3"/>
+      <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
       <c r="D248" s="2"/>
@@ -8489,7 +8576,7 @@
       <c r="AB248" s="1"/>
     </row>
     <row r="249" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A249" s="3"/>
+      <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
       <c r="D249" s="2"/>
@@ -8519,7 +8606,7 @@
       <c r="AB249" s="1"/>
     </row>
     <row r="250" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A250" s="3"/>
+      <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
       <c r="D250" s="2"/>
@@ -8549,7 +8636,7 @@
       <c r="AB250" s="1"/>
     </row>
     <row r="251" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A251" s="3"/>
+      <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
       <c r="D251" s="2"/>
@@ -8579,7 +8666,7 @@
       <c r="AB251" s="1"/>
     </row>
     <row r="252" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A252" s="3"/>
+      <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
       <c r="D252" s="2"/>
@@ -8609,7 +8696,7 @@
       <c r="AB252" s="1"/>
     </row>
     <row r="253" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A253" s="3"/>
+      <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
       <c r="D253" s="2"/>
@@ -8639,7 +8726,7 @@
       <c r="AB253" s="1"/>
     </row>
     <row r="254" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A254" s="3"/>
+      <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
       <c r="D254" s="2"/>
@@ -8669,7 +8756,7 @@
       <c r="AB254" s="1"/>
     </row>
     <row r="255" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A255" s="3"/>
+      <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
       <c r="D255" s="2"/>
@@ -8699,7 +8786,7 @@
       <c r="AB255" s="1"/>
     </row>
     <row r="256" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A256" s="3"/>
+      <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
       <c r="D256" s="2"/>
@@ -8729,7 +8816,7 @@
       <c r="AB256" s="1"/>
     </row>
     <row r="257" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A257" s="3"/>
+      <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
       <c r="D257" s="2"/>
@@ -8759,7 +8846,7 @@
       <c r="AB257" s="1"/>
     </row>
     <row r="258" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A258" s="3"/>
+      <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
       <c r="D258" s="2"/>
@@ -8789,7 +8876,7 @@
       <c r="AB258" s="1"/>
     </row>
     <row r="259" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A259" s="3"/>
+      <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
       <c r="D259" s="2"/>
@@ -8819,7 +8906,7 @@
       <c r="AB259" s="1"/>
     </row>
     <row r="260" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A260" s="3"/>
+      <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
       <c r="D260" s="2"/>
@@ -8849,7 +8936,7 @@
       <c r="AB260" s="1"/>
     </row>
     <row r="261" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A261" s="3"/>
+      <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
       <c r="D261" s="2"/>
@@ -8879,7 +8966,7 @@
       <c r="AB261" s="1"/>
     </row>
     <row r="262" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A262" s="3"/>
+      <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
       <c r="D262" s="2"/>
@@ -8909,7 +8996,7 @@
       <c r="AB262" s="1"/>
     </row>
     <row r="263" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A263" s="3"/>
+      <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
       <c r="D263" s="2"/>
@@ -8939,7 +9026,7 @@
       <c r="AB263" s="1"/>
     </row>
     <row r="264" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A264" s="3"/>
+      <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
       <c r="D264" s="2"/>
@@ -8969,7 +9056,7 @@
       <c r="AB264" s="1"/>
     </row>
     <row r="265" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A265" s="3"/>
+      <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
       <c r="D265" s="2"/>
@@ -8999,7 +9086,7 @@
       <c r="AB265" s="1"/>
     </row>
     <row r="266" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A266" s="3"/>
+      <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
       <c r="D266" s="2"/>
@@ -9029,7 +9116,7 @@
       <c r="AB266" s="1"/>
     </row>
     <row r="267" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A267" s="3"/>
+      <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
       <c r="D267" s="2"/>
@@ -9059,7 +9146,7 @@
       <c r="AB267" s="1"/>
     </row>
     <row r="268" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A268" s="3"/>
+      <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
       <c r="D268" s="2"/>
@@ -9089,7 +9176,7 @@
       <c r="AB268" s="1"/>
     </row>
     <row r="269" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A269" s="3"/>
+      <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
       <c r="D269" s="2"/>
@@ -9119,7 +9206,7 @@
       <c r="AB269" s="1"/>
     </row>
     <row r="270" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A270" s="3"/>
+      <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
       <c r="D270" s="2"/>
@@ -9149,7 +9236,7 @@
       <c r="AB270" s="1"/>
     </row>
     <row r="271" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A271" s="3"/>
+      <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
       <c r="D271" s="2"/>
@@ -9179,7 +9266,7 @@
       <c r="AB271" s="1"/>
     </row>
     <row r="272" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A272" s="3"/>
+      <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
       <c r="D272" s="2"/>
@@ -9209,7 +9296,7 @@
       <c r="AB272" s="1"/>
     </row>
     <row r="273" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A273" s="3"/>
+      <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
@@ -9239,7 +9326,7 @@
       <c r="AB273" s="1"/>
     </row>
     <row r="274" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A274" s="3"/>
+      <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
       <c r="D274" s="2"/>
@@ -9269,7 +9356,7 @@
       <c r="AB274" s="1"/>
     </row>
     <row r="275" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A275" s="3"/>
+      <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
       <c r="D275" s="2"/>
@@ -9299,7 +9386,7 @@
       <c r="AB275" s="1"/>
     </row>
     <row r="276" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A276" s="3"/>
+      <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
       <c r="D276" s="2"/>
@@ -9329,7 +9416,7 @@
       <c r="AB276" s="1"/>
     </row>
     <row r="277" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A277" s="3"/>
+      <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
       <c r="D277" s="2"/>
@@ -9359,7 +9446,7 @@
       <c r="AB277" s="1"/>
     </row>
     <row r="278" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A278" s="3"/>
+      <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
       <c r="D278" s="2"/>
@@ -9389,7 +9476,7 @@
       <c r="AB278" s="1"/>
     </row>
     <row r="279" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A279" s="3"/>
+      <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
       <c r="D279" s="2"/>
@@ -9419,7 +9506,7 @@
       <c r="AB279" s="1"/>
     </row>
     <row r="280" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A280" s="3"/>
+      <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
       <c r="D280" s="2"/>
@@ -9449,7 +9536,7 @@
       <c r="AB280" s="1"/>
     </row>
     <row r="281" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A281" s="3"/>
+      <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
       <c r="D281" s="2"/>
@@ -9479,7 +9566,7 @@
       <c r="AB281" s="1"/>
     </row>
     <row r="282" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A282" s="3"/>
+      <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
       <c r="D282" s="2"/>
@@ -9509,7 +9596,7 @@
       <c r="AB282" s="1"/>
     </row>
     <row r="283" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A283" s="3"/>
+      <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
       <c r="D283" s="2"/>
@@ -9539,7 +9626,7 @@
       <c r="AB283" s="1"/>
     </row>
     <row r="284" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A284" s="3"/>
+      <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
       <c r="D284" s="2"/>
@@ -9569,7 +9656,7 @@
       <c r="AB284" s="1"/>
     </row>
     <row r="285" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A285" s="3"/>
+      <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
       <c r="D285" s="2"/>
@@ -9599,7 +9686,7 @@
       <c r="AB285" s="1"/>
     </row>
     <row r="286" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A286" s="4"/>
+      <c r="A286" s="3"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
       <c r="D286" s="2"/>

--- a/Datos/Datos_Necesitamos.xlsx
+++ b/Datos/Datos_Necesitamos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NICO\Desktop\Universidad\Practicas\Practicas-2026-Nicolas-Garcia-Gomez\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4937F688-A724-4D93-8F3E-7E257281B588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49B338A-1A11-439C-B917-89E1A670A51F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="75">
   <si>
     <t>Reingresos no programados en URCCPQ</t>
   </si>
@@ -183,15 +183,6 @@
       </rPr>
       <t>)</t>
     </r>
-  </si>
-  <si>
-    <t>Alta precoz o no planificada del servicio de medicina intensiva</t>
-  </si>
-  <si>
-    <t>(Num de enfermos con alta precoz o no planificada del SMI</t>
-  </si>
-  <si>
-    <t>Total de altas)</t>
   </si>
   <si>
     <t>Resucitacion precoz de la sepsis</t>
@@ -469,6 +460,27 @@
   <si>
     <t>Num total de días de TET) = vmi</t>
   </si>
+  <si>
+    <t>Problemas</t>
+  </si>
+  <si>
+    <t>Listado de verificacion</t>
+  </si>
+  <si>
+    <t>Cuagulopatia</t>
+  </si>
+  <si>
+    <t>Sedacion continuada vale con tener RASS o BIS</t>
+  </si>
+  <si>
+    <t>Cantidad de trasfusion</t>
+  </si>
+  <si>
+    <t>Resucitacion precoz = 3 parametros nuevos</t>
+  </si>
+  <si>
+    <t>Biogram al inicio y al final</t>
+  </si>
 </sst>
 </file>
 
@@ -497,7 +509,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -531,6 +543,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,7 +589,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -616,6 +634,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -898,17 +922,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB476"/>
+  <dimension ref="A1:AB475"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="68.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="118.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="106.21875" customWidth="1"/>
     <col min="4" max="4" width="50.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -921,7 +947,9 @@
         <v>3</v>
       </c>
       <c r="E1" s="6"/>
-      <c r="F1" s="1"/>
+      <c r="F1" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -946,7 +974,7 @@
       <c r="AB1" s="1"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="17" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -961,7 +989,7 @@
       <c r="E2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="1"/>
+      <c r="F2" s="6"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -986,11 +1014,11 @@
       <c r="AB2" s="1"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>5</v>
@@ -1001,7 +1029,7 @@
       <c r="E3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1"/>
+      <c r="F3" s="6"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -1026,7 +1054,7 @@
       <c r="AB3" s="1"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="17" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="9" t="s">
@@ -1041,7 +1069,7 @@
       <c r="E4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="1"/>
+      <c r="F4" s="6"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -1066,11 +1094,11 @@
       <c r="AB4" s="1"/>
     </row>
     <row r="5" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="17" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>5</v>
@@ -1081,7 +1109,7 @@
       <c r="E5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="1"/>
+      <c r="F5" s="8"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -1106,7 +1134,7 @@
       <c r="AB5" s="1"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -1121,7 +1149,7 @@
       <c r="E6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="1"/>
+      <c r="F6" s="6"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -1146,7 +1174,7 @@
       <c r="AB6" s="1"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="17" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="9" t="s">
@@ -1161,7 +1189,7 @@
       <c r="E7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="1"/>
+      <c r="F7" s="6"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -1189,20 +1217,22 @@
       <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="9" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+      <c r="F8" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="16"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -1229,19 +1259,21 @@
       <c r="A9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="1"/>
+      <c r="F9" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -1269,19 +1301,21 @@
       <c r="A10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>29</v>
+      <c r="B10" s="9" t="s">
+        <v>62</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>30</v>
+      <c r="D10" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="1"/>
+      <c r="F10" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -1306,22 +1340,22 @@
       <c r="AB10" s="1"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>31</v>
+      <c r="A11" s="17" t="s">
+        <v>30</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>65</v>
+      <c r="B11" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>32</v>
+      <c r="D11" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="1"/>
+      <c r="F11" s="6"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -1347,21 +1381,23 @@
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>60</v>
+      <c r="B12" s="10" t="s">
+        <v>63</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>69</v>
+      <c r="D12" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="1"/>
+      <c r="F12" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -1386,22 +1422,22 @@
       <c r="AB12" s="1"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>66</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>5</v>
       </c>
       <c r="D13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="1"/>
+      <c r="F13" s="6"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -1429,19 +1465,21 @@
       <c r="A14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>37</v>
+      <c r="B14" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>5</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
-      <c r="F14" s="1"/>
+      <c r="F14" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -1466,22 +1504,22 @@
       <c r="AB14" s="1"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>67</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>40</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="1"/>
+      <c r="F15" s="6"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -1515,13 +1553,13 @@
       <c r="C16" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>43</v>
+      <c r="D16" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="1"/>
+      <c r="F16" s="6"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -1547,10 +1585,10 @@
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>5</v>
@@ -1561,7 +1599,7 @@
       <c r="E17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="1"/>
+      <c r="F17" s="6"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -1587,21 +1625,21 @@
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>5</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="1"/>
+      <c r="F18" s="6"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1627,21 +1665,21 @@
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>5</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F19" s="1"/>
+      <c r="F19" s="6"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -1667,10 +1705,10 @@
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>48</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>68</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>5</v>
@@ -1681,7 +1719,9 @@
       <c r="E20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="1"/>
+      <c r="F20" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -1709,19 +1749,19 @@
       <c r="A21" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>51</v>
+      <c r="B21" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>52</v>
+      <c r="D21" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
-      <c r="F21" s="1"/>
+      <c r="F21" s="6"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -1746,21 +1786,15 @@
       <c r="AB21" s="1"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>53</v>
+      <c r="A22" s="11" t="s">
+        <v>51</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>63</v>
+      <c r="B22" s="12" t="s">
+        <v>54</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>6</v>
-      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -1786,11 +1820,11 @@
       <c r="AB22" s="1"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
-        <v>54</v>
+      <c r="A23" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -1820,12 +1854,10 @@
       <c r="AB23" s="1"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A24" s="13" t="s">
-        <v>55</v>
+      <c r="A24" s="14" t="s">
+        <v>53</v>
       </c>
-      <c r="B24" s="12" t="s">
-        <v>58</v>
-      </c>
+      <c r="B24" s="15"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -1854,10 +1886,8 @@
       <c r="AB24" s="1"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="15"/>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -9656,7 +9686,7 @@
       <c r="AB284" s="1"/>
     </row>
     <row r="285" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A285" s="2"/>
+      <c r="A285" s="3"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
       <c r="D285" s="2"/>
@@ -9686,7 +9716,7 @@
       <c r="AB285" s="1"/>
     </row>
     <row r="286" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A286" s="3"/>
+      <c r="A286" s="1"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
       <c r="D286" s="2"/>
@@ -10077,10 +10107,10 @@
     </row>
     <row r="299" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A299" s="1"/>
-      <c r="B299" s="2"/>
-      <c r="C299" s="2"/>
-      <c r="D299" s="2"/>
-      <c r="E299" s="2"/>
+      <c r="B299" s="1"/>
+      <c r="C299" s="1"/>
+      <c r="D299" s="1"/>
+      <c r="E299" s="1"/>
       <c r="F299" s="1"/>
       <c r="G299" s="1"/>
       <c r="H299" s="1"/>
@@ -15385,36 +15415,6 @@
       <c r="AA475" s="1"/>
       <c r="AB475" s="1"/>
     </row>
-    <row r="476" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A476" s="1"/>
-      <c r="B476" s="1"/>
-      <c r="C476" s="1"/>
-      <c r="D476" s="1"/>
-      <c r="E476" s="1"/>
-      <c r="F476" s="1"/>
-      <c r="G476" s="1"/>
-      <c r="H476" s="1"/>
-      <c r="I476" s="1"/>
-      <c r="J476" s="1"/>
-      <c r="K476" s="1"/>
-      <c r="L476" s="1"/>
-      <c r="M476" s="1"/>
-      <c r="N476" s="1"/>
-      <c r="O476" s="1"/>
-      <c r="P476" s="1"/>
-      <c r="Q476" s="1"/>
-      <c r="R476" s="1"/>
-      <c r="S476" s="1"/>
-      <c r="T476" s="1"/>
-      <c r="U476" s="1"/>
-      <c r="V476" s="1"/>
-      <c r="W476" s="1"/>
-      <c r="X476" s="1"/>
-      <c r="Y476" s="1"/>
-      <c r="Z476" s="1"/>
-      <c r="AA476" s="1"/>
-      <c r="AB476" s="1"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datos/Datos_Necesitamos.xlsx
+++ b/Datos/Datos_Necesitamos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NICO\Desktop\Universidad\Practicas\Practicas-2026-Nicolas-Garcia-Gomez\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49B338A-1A11-439C-B917-89E1A670A51F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51341F38-B2BF-48A6-8736-95281845EE66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="73">
   <si>
     <t>Reingresos no programados en URCCPQ</t>
   </si>
@@ -461,25 +461,19 @@
     <t>Num total de días de TET) = vmi</t>
   </si>
   <si>
-    <t>Problemas</t>
-  </si>
-  <si>
-    <t>Listado de verificacion</t>
-  </si>
-  <si>
-    <t>Cuagulopatia</t>
-  </si>
-  <si>
-    <t>Sedacion continuada vale con tener RASS o BIS</t>
-  </si>
-  <si>
     <t>Cantidad de trasfusion</t>
   </si>
   <si>
-    <t>Resucitacion precoz = 3 parametros nuevos</t>
+    <t>PREGUNTAR: si esta bien(SS o sepsis) y los 3 a la vez de la recuperacion</t>
   </si>
   <si>
-    <t>Biogram al inicio y al final</t>
+    <t>PREGUNTAR: tienen que coincidir todos los antibioticos o solo uno</t>
+  </si>
+  <si>
+    <t>PREGUNTAR: todos a la vez o con uno vale en HGI y PROFILAXIS varias</t>
+  </si>
+  <si>
+    <t>PREGUNTAR: como saber si es sedacion adecuada</t>
   </si>
 </sst>
 </file>
@@ -926,11 +920,11 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="68.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="106.21875" customWidth="1"/>
+    <col min="2" max="2" width="113.88671875" customWidth="1"/>
     <col min="4" max="4" width="50.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="59.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -947,9 +941,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="6"/>
-      <c r="F1" s="6" t="s">
-        <v>68</v>
-      </c>
+      <c r="F1" s="6"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -1214,7 +1206,7 @@
       <c r="AB7" s="1"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="17" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="9" t="s">
@@ -1230,7 +1222,7 @@
         <v>9</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="1"/>
@@ -1256,7 +1248,7 @@
       <c r="AB8" s="1"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -1271,9 +1263,7 @@
       <c r="E9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>69</v>
-      </c>
+      <c r="F9" s="8"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -1298,7 +1288,7 @@
       <c r="AB9" s="1"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="17" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="9" t="s">
@@ -1314,7 +1304,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -1380,7 +1370,7 @@
       <c r="AB11" s="1"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B12" s="10" t="s">
@@ -1396,7 +1386,7 @@
         <v>9</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1462,7 +1452,7 @@
       <c r="AB13" s="1"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="17" t="s">
         <v>36</v>
       </c>
       <c r="B14" s="9" t="s">
@@ -1478,7 +1468,7 @@
         <v>9</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -1720,7 +1710,7 @@
         <v>9</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>

--- a/Datos/Datos_Necesitamos.xlsx
+++ b/Datos/Datos_Necesitamos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NICO\Desktop\Universidad\Practicas\Practicas-2026-Nicolas-Garcia-Gomez\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51341F38-B2BF-48A6-8736-95281845EE66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D1E64A-E1EC-4824-A545-CD60BA81E676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="72">
   <si>
     <t>Reingresos no programados en URCCPQ</t>
   </si>
@@ -459,9 +459,6 @@
   </si>
   <si>
     <t>Num total de días de TET) = vmi</t>
-  </si>
-  <si>
-    <t>Cantidad de trasfusion</t>
   </si>
   <si>
     <t>PREGUNTAR: si esta bien(SS o sepsis) y los 3 a la vez de la recuperacion</t>
@@ -1222,7 +1219,7 @@
         <v>9</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="1"/>
@@ -1304,7 +1301,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -1386,7 +1383,7 @@
         <v>9</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1468,7 +1465,7 @@
         <v>9</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -1574,7 +1571,7 @@
       <c r="AB16" s="1"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="17" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -1614,7 +1611,7 @@
       <c r="AB17" s="1"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="17" t="s">
         <v>44</v>
       </c>
       <c r="B18" s="5" t="s">
@@ -1654,7 +1651,7 @@
       <c r="AB18" s="1"/>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="17" t="s">
         <v>45</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -1694,7 +1691,7 @@
       <c r="AB19" s="1"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="17" t="s">
         <v>47</v>
       </c>
       <c r="B20" s="9" t="s">
@@ -1709,9 +1706,7 @@
       <c r="E20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>68</v>
-      </c>
+      <c r="F20" s="8"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -1736,7 +1731,7 @@
       <c r="AB20" s="1"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="17" t="s">
         <v>50</v>
       </c>
       <c r="B21" s="5" t="s">

--- a/Datos/Datos_Necesitamos.xlsx
+++ b/Datos/Datos_Necesitamos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NICO\Desktop\Universidad\Practicas\Practicas-2026-Nicolas-Garcia-Gomez\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D1E64A-E1EC-4824-A545-CD60BA81E676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50DC183D-BE1D-4589-8B50-E3D32605535C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="68">
   <si>
     <t>Reingresos no programados en URCCPQ</t>
   </si>
@@ -460,18 +460,6 @@
   <si>
     <t>Num total de días de TET) = vmi</t>
   </si>
-  <si>
-    <t>PREGUNTAR: si esta bien(SS o sepsis) y los 3 a la vez de la recuperacion</t>
-  </si>
-  <si>
-    <t>PREGUNTAR: tienen que coincidir todos los antibioticos o solo uno</t>
-  </si>
-  <si>
-    <t>PREGUNTAR: todos a la vez o con uno vale en HGI y PROFILAXIS varias</t>
-  </si>
-  <si>
-    <t>PREGUNTAR: como saber si es sedacion adecuada</t>
-  </si>
 </sst>
 </file>
 
@@ -500,18 +488,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -580,12 +562,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -594,14 +576,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -609,7 +591,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -621,16 +603,13 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -917,28 +896,28 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="68.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="113.88671875" customWidth="1"/>
+    <col min="2" max="2" width="112.44140625" customWidth="1"/>
     <col min="4" max="4" width="50.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="59.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" customWidth="1"/>
+    <col min="7" max="7" width="48.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -963,22 +942,22 @@
       <c r="AB1" s="1"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="6"/>
+      <c r="F2" s="5"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -1003,22 +982,22 @@
       <c r="AB2" s="1"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="6"/>
+      <c r="F3" s="5"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -1043,22 +1022,22 @@
       <c r="AB3" s="1"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="6"/>
+      <c r="F4" s="5"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -1083,22 +1062,22 @@
       <c r="AB4" s="1"/>
     </row>
     <row r="5" spans="1:28" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="8"/>
+      <c r="F5" s="7"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -1123,22 +1102,22 @@
       <c r="AB5" s="1"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="6"/>
+      <c r="F6" s="5"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -1163,22 +1142,22 @@
       <c r="AB6" s="1"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="6"/>
+      <c r="F7" s="5"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -1203,25 +1182,23 @@
       <c r="AB7" s="1"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="16"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="15"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -1245,22 +1222,22 @@
       <c r="AB8" s="1"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="8"/>
+      <c r="F9" s="7"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -1285,24 +1262,22 @@
       <c r="AB9" s="1"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>69</v>
-      </c>
+      <c r="F10" s="7"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -1327,22 +1302,22 @@
       <c r="AB10" s="1"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="6"/>
+      <c r="F11" s="5"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -1367,24 +1342,22 @@
       <c r="AB11" s="1"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>70</v>
-      </c>
+      <c r="F12" s="7"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -1409,22 +1382,22 @@
       <c r="AB12" s="1"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="6"/>
+      <c r="F13" s="5"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -1449,24 +1422,22 @@
       <c r="AB13" s="1"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>71</v>
-      </c>
+      <c r="F14" s="7"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -1491,22 +1462,22 @@
       <c r="AB14" s="1"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="6"/>
+      <c r="F15" s="5"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -1531,22 +1502,22 @@
       <c r="AB15" s="1"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="6"/>
+      <c r="F16" s="5"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -1571,22 +1542,22 @@
       <c r="AB16" s="1"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="6"/>
+      <c r="F17" s="5"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -1611,22 +1582,22 @@
       <c r="AB17" s="1"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="6"/>
+      <c r="F18" s="5"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1651,22 +1622,22 @@
       <c r="AB18" s="1"/>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F19" s="6"/>
+      <c r="F19" s="5"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -1691,22 +1662,22 @@
       <c r="AB19" s="1"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="8"/>
+      <c r="F20" s="7"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -1731,22 +1702,22 @@
       <c r="AB20" s="1"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F21" s="6"/>
+      <c r="F21" s="5"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -1771,10 +1742,10 @@
       <c r="AB21" s="1"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="11" t="s">
         <v>54</v>
       </c>
       <c r="C22" s="2"/>
@@ -1805,10 +1776,10 @@
       <c r="AB22" s="1"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="11" t="s">
         <v>55</v>
       </c>
       <c r="C23" s="2"/>
@@ -1839,10 +1810,10 @@
       <c r="AB23" s="1"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="15"/>
+      <c r="B24" s="14"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>

--- a/Datos/Datos_Necesitamos.xlsx
+++ b/Datos/Datos_Necesitamos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NICO\Desktop\Universidad\Practicas\Practicas-2026-Nicolas-Garcia-Gomez\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50DC183D-BE1D-4589-8B50-E3D32605535C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A164D693-29AB-4A99-92BC-6D425073A5D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="69">
   <si>
     <t>Reingresos no programados en URCCPQ</t>
   </si>
@@ -460,6 +460,9 @@
   <si>
     <t>Num total de días de TET) = vmi</t>
   </si>
+  <si>
+    <t>ventana de sedacion es un numero</t>
+  </si>
 </sst>
 </file>
 
@@ -488,7 +491,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -522,6 +525,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -562,7 +571,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -610,6 +619,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1077,7 +1089,9 @@
       <c r="E5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="7"/>
+      <c r="F5" s="17" t="s">
+        <v>68</v>
+      </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -1157,7 +1171,7 @@
       <c r="E7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="5"/>
+      <c r="F7" s="7"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>

--- a/Datos/Datos_Necesitamos.xlsx
+++ b/Datos/Datos_Necesitamos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NICO\Desktop\Universidad\Practicas\Practicas-2026-Nicolas-Garcia-Gomez\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A164D693-29AB-4A99-92BC-6D425073A5D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739DF0D0-B9D7-4531-972B-2E7612D55EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="68">
   <si>
     <t>Reingresos no programados en URCCPQ</t>
   </si>
@@ -460,9 +460,6 @@
   <si>
     <t>Num total de días de TET) = vmi</t>
   </si>
-  <si>
-    <t>ventana de sedacion es un numero</t>
-  </si>
 </sst>
 </file>
 
@@ -491,7 +488,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -525,12 +522,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,7 +562,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -619,9 +610,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1089,9 +1077,7 @@
       <c r="E5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="17" t="s">
-        <v>68</v>
-      </c>
+      <c r="F5" s="7"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
